--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487457_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487457_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.4752</v>
+        <v>13.1045</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7157</v>
+        <v>11.4252</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7595</v>
+        <v>1.6793</v>
       </c>
       <c r="G2" t="n">
         <v>9.2187</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>0.457</v>
+        <v>0.0863</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5023</v>
+        <v>0.2117</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0452</v>
+        <v>-0.1254</v>
       </c>
       <c r="V2" t="n">
         <v>0.6659</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1702</v>
+        <v>5.1435</v>
       </c>
       <c r="E3" t="n">
         <v>3.9593</v>
       </c>
       <c r="F3" t="n">
-        <v>1.211</v>
+        <v>1.1842</v>
       </c>
       <c r="G3" t="n">
         <v>2.7961</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2198</v>
+        <v>0.1931</v>
       </c>
       <c r="T3" t="n">
         <v>0.0288</v>
       </c>
       <c r="U3" t="n">
-        <v>0.191</v>
+        <v>0.1642</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9375</v>
+        <v>4.5419</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0407</v>
+        <v>2.5288</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1032</v>
+        <v>2.0131</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7954</v>
+        <v>3.2831</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6226</v>
+        <v>-2.6679</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1728</v>
+        <v>5.951</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0371</v>
+        <v>3.5957</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4361</v>
+        <v>-1.5159</v>
       </c>
       <c r="L4" t="n">
-        <v>2.601</v>
+        <v>5.1116</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2417</v>
+        <v>-0.3126</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8135</v>
+        <v>-1.152</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5717</v>
+        <v>0.8394</v>
       </c>
       <c r="P4" t="n">
+        <v>1.5668</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4543</v>
+        <v>-0.6409</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2327</v>
+        <v>-0.0876</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2216</v>
+        <v>-0.5533</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3329</v>
+        <v>0.3329</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.0415</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1651</v>
+        <v>4.1911</v>
       </c>
       <c r="E5" t="n">
-        <v>1.446</v>
+        <v>5.5884</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7191</v>
+        <v>-1.3972</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2831</v>
+        <v>4.7954</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.6679</v>
+        <v>1.6226</v>
       </c>
       <c r="I5" t="n">
-        <v>5.951</v>
+        <v>3.1728</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5957</v>
+        <v>5.0371</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5159</v>
+        <v>2.4361</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1116</v>
+        <v>2.601</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3126</v>
+        <v>-0.2417</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.152</v>
+        <v>-0.8135</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8394</v>
+        <v>0.5717</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0177</v>
+        <v>0.708</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1704</v>
+        <v>0.7804</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3329</v>
+        <v>-0.3329</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3329</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0727</v>
+        <v>1.7448</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6073</v>
+        <v>1.119</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4654</v>
+        <v>0.6258</v>
       </c>
       <c r="G6" t="n">
         <v>3.0839</v>
@@ -922,13 +922,13 @@
         <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0475</v>
+        <v>0.7196</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2535</v>
+        <v>0.7652</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.206</v>
+        <v>-0.0456</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8837</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6975</v>
+        <v>1.3709</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3614</v>
+        <v>0.312</v>
       </c>
       <c r="F7" t="n">
         <v>1.0589</v>
@@ -1000,10 +1000,10 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3499</v>
+        <v>0.3235</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6952</v>
+        <v>-0.0218</v>
       </c>
       <c r="U7" t="n">
         <v>0.3452</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>J. MANEIRO SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4877</v>
+        <v>0.3026</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5844</v>
+        <v>-0.0594</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0967</v>
+        <v>0.362</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4641</v>
+        <v>0.4093</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.096</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6318</v>
+        <v>0.4093</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0723</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0808</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5364</v>
+        <v>0.4093</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0874</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.551</v>
+        <v>0.4093</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9726</v>
+        <v>-0.1067</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5121</v>
+        <v>-0.0594</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5395</v>
+        <v>-0.0473</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MANEIRO SANCHEZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2491</v>
+        <v>-0.4436</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0594</v>
+        <v>0.6798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3085</v>
+        <v>-1.1234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4093</v>
+        <v>-0.4641</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-1.096</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4093</v>
+        <v>0.6318</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0723</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4093</v>
+        <v>-0.5364</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.0874</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4093</v>
+        <v>0.551</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1602</v>
+        <v>0.0413</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0594</v>
+        <v>0.6075</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1008</v>
+        <v>-0.5662</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7294</v>
+        <v>-2.8526</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8294</v>
+        <v>-3.8723</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.0198</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3417</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2194</v>
+        <v>0.0963</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4734</v>
+        <v>0.4305</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.254</v>
+        <v>-0.3342</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6071</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7151</v>
+        <v>-3.6986</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7519</v>
+        <v>-2.7354</v>
       </c>
       <c r="F11" t="n">
         <v>-0.9631999999999999</v>
@@ -1312,10 +1312,10 @@
         <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1364</v>
+        <v>0.1529</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2247</v>
+        <v>0.2411</v>
       </c>
       <c r="U11" t="n">
         <v>-0.0882</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>22.8105</v>
+        <v>23.4045</v>
       </c>
       <c r="E12" t="n">
-        <v>18.3513</v>
+        <v>18.9454</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4593</v>
+        <v>4.459300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>20.2336</v>
@@ -1390,13 +1390,13 @@
         <v>16.647</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9792</v>
+        <v>1.5734</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3025</v>
+        <v>2.8964</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3232</v>
+        <v>-1.3233</v>
       </c>
       <c r="V12" t="n">
         <v>-5.2569</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2106</v>
+        <v>1.8178</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9021</v>
+        <v>3.1857</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6915</v>
+        <v>-1.3679</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2178</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8005</v>
+        <v>0.4077</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3868</v>
+        <v>0.6705</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5863</v>
+        <v>-0.2627</v>
       </c>
       <c r="V13" t="n">
         <v>2.2154</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0429</v>
+        <v>1.1144</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0192</v>
+        <v>0.0195</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9763</v>
+        <v>1.0949</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5446</v>
+        <v>0.2716</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9251</v>
+        <v>0.13</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.4698</v>
+        <v>0.1416</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0136</v>
+        <v>0.0612</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2813</v>
+        <v>0.0612</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7323</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.5582</v>
+        <v>0.2104</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3562</v>
+        <v>0.0687</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.2021</v>
+        <v>0.1416</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0588</v>
+        <v>0.2553</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3178</v>
+        <v>-0.0418</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2591</v>
+        <v>0.297</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.978</v>
+        <v>1.0193</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0195</v>
+        <v>1.2037</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9585</v>
+        <v>-0.1844</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2716</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.13</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1416</v>
+        <v>-0.2773</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0612</v>
+        <v>2.7648</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0612</v>
+        <v>1.9921</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2104</v>
+        <v>-2.1354</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0687</v>
+        <v>-1.0853</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1416</v>
+        <v>-1.0501</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1188</v>
+        <v>-0.2404</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0418</v>
+        <v>-0.4288</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1606</v>
+        <v>0.1884</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1795</v>
+        <v>-0.3818</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7943</v>
+        <v>0.0265</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6149</v>
+        <v>-0.4083</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6294999999999999</v>
+        <v>-0.1354</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9068000000000001</v>
+        <v>-0.2719</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2773</v>
+        <v>0.1364</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7648</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9921</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7727000000000001</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1354</v>
+        <v>-0.1354</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0853</v>
+        <v>-0.2719</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0501</v>
+        <v>0.1364</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0802</v>
+        <v>-0.2464</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8381</v>
+        <v>0.0265</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2421</v>
+        <v>-0.2729</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5865</v>
+        <v>-0.4211</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1782</v>
+        <v>2.6889</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4083</v>
+        <v>-3.11</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1354</v>
+        <v>-1.5446</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2719</v>
+        <v>0.9251</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1364</v>
+        <v>-2.4698</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.0136</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.2813</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.7323</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1354</v>
+        <v>-4.5582</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2719</v>
+        <v>-1.3562</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1364</v>
+        <v>-3.2021</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4511</v>
+        <v>0.5948</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1782</v>
+        <v>0.9875</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2729</v>
+        <v>-0.3927</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.498</v>
+        <v>-0.8905</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1305</v>
+        <v>-0.2822</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6286</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2911</v>
+        <v>-3.8962</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6901</v>
+        <v>-1.8599</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.399</v>
+        <v>-2.0363</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3474</v>
+        <v>-3.0233</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3474</v>
+        <v>-0.9766</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.0467</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0563</v>
+        <v>-0.8729</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3427</v>
+        <v>-0.8833</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.399</v>
+        <v>0.0104</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7892</v>
+        <v>-0.2525</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2376</v>
+        <v>0.0706</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5516</v>
+        <v>-0.323</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2166</v>
+        <v>3.6498</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.6498</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.57</v>
+        <v>-1.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6915</v>
+        <v>0.3352</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-1.5217</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8962</v>
+        <v>1.2911</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8599</v>
+        <v>1.6901</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0363</v>
+        <v>-0.399</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.0233</v>
+        <v>1.3474</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9766</v>
+        <v>1.3474</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0467</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8729</v>
+        <v>-0.0563</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8833</v>
+        <v>0.3427</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0104</v>
+        <v>-0.399</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9319</v>
+        <v>-0.4776</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3388</v>
+        <v>-0.0329</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5931</v>
+        <v>-0.4446</v>
       </c>
       <c r="V19" t="n">
-        <v>3.6498</v>
+        <v>-1.2166</v>
       </c>
       <c r="W19" t="n">
-        <v>3.6498</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5142</v>
+        <v>-2.4312</v>
       </c>
       <c r="E20" t="n">
         <v>-3.2438</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7296</v>
+        <v>0.8126</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4028</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0061</v>
+        <v>0.0891</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2794</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2855</v>
+        <v>0.3685</v>
       </c>
       <c r="V20" t="n">
         <v>0.0576</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5027</v>
+        <v>-3.5478</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4147</v>
+        <v>-1.0054</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.088</v>
+        <v>-2.5424</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4342</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3393</v>
+        <v>0.2942</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3517</v>
+        <v>0.0576</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.2366</v>
       </c>
       <c r="V21" t="n">
         <v>1.159</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9681</v>
+        <v>-4.3487</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0383</v>
+        <v>-0.8753</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9299</v>
+        <v>-3.4734</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7791</v>
+        <v>-1.6949</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8548</v>
+        <v>-1.1895</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9244</v>
+        <v>-0.5054</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2865</v>
+        <v>-0.0095</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2914</v>
+        <v>0.1021</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0048</v>
+        <v>-0.1116</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4926</v>
+        <v>-1.6853</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5634</v>
+        <v>-1.2916</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9292</v>
+        <v>-0.3938</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3502</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>0.22</v>
+        <v>-0.3785</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0306</v>
+        <v>0.1135</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2506</v>
+        <v>-0.492</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9412</v>
+        <v>-1.492</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0208</v>
+        <v>-5.1331</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3869</v>
+        <v>-2.9359</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6338</v>
+        <v>-2.1972</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6949</v>
+        <v>-3.7791</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1895</v>
+        <v>-2.8548</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5054</v>
+        <v>-0.9244</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0095</v>
+        <v>-1.2865</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1021</v>
+        <v>-1.2914</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1116</v>
+        <v>0.0048</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6853</v>
+        <v>-2.4926</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2916</v>
+        <v>-1.5634</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3938</v>
+        <v>-0.9292</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7834</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0505</v>
+        <v>0.055</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3982</v>
+        <v>0.0717</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6524</v>
+        <v>-0.0168</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.492</v>
+        <v>0.9412</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5612</v>
+        <v>-7.7391</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3714</v>
+        <v>-3.5761</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1897</v>
+        <v>-4.163</v>
       </c>
       <c r="G24" t="n">
         <v>-6.3206</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2198</v>
+        <v>-0.3977</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3129</v>
+        <v>0.1082</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5327</v>
+        <v>-0.5059</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2166</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-22.8105</v>
+        <v>-22.1283</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4592</v>
+        <v>-4.459200000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.3514</v>
+        <v>-17.6692</v>
       </c>
       <c r="G25" t="n">
         <v>-20.2334</v>
@@ -2401,16 +2401,16 @@
         <v>-16.6469</v>
       </c>
       <c r="R25" t="n">
-        <v>9.792100000000001</v>
+        <v>9.7921</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9792</v>
+        <v>-0.297</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3231</v>
+        <v>1.3232</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.3025</v>
+        <v>-1.6201</v>
       </c>
       <c r="V25" t="n">
         <v>5.2568</v>
